--- a/data/flo/fabric-invoice-numbers.xlsx
+++ b/data/flo/fabric-invoice-numbers.xlsx
@@ -34,7 +34,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -68,14 +68,14 @@
   </cellStyleXfs>
   <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -385,39 +385,35 @@
     <col min="1" max="1" style="3" width="14.147857142857141" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="2">
-        <v>1010033794</v>
+        <v>1010050400</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="2">
-        <v>1010033795</v>
+        <v>1010050399</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
-      <c r="A4" s="2">
-        <v>1010033798</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
-      <c r="A5" s="2">
-        <v>1010033800</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
-      <c r="A6" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
-      <c r="A7" s="1"/>
-    </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
-      <c r="A8" s="1"/>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
+      <c r="A4" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
+      <c r="A5" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
+      <c r="A6" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
+      <c r="A7" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
+      <c r="A8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
